--- a/data/trans_dic/P19F$mañana-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19F$mañana-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la mañana</t>
+          <t>Población que, al menos, se cepilla los dientes por la mañana (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,43; 52,97</t>
+          <t>37,89; 52,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,84; 58,18</t>
+          <t>41,2; 58,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,97; 53,47</t>
+          <t>41,57; 52,32</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,68; 46,79</t>
+          <t>32,39; 47,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,04; 53,6</t>
+          <t>37,77; 53,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,58; 47,7</t>
+          <t>37,51; 48,12</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,21; 46,81</t>
+          <t>34,89; 46,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,45; 64,64</t>
+          <t>41,74; 64,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,51; 49,37</t>
+          <t>38,22; 48,7</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,8; 44,04</t>
+          <t>35,54; 43,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,49; 52,8</t>
+          <t>43,37; 52,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,84; 46,19</t>
+          <t>39,86; 45,94</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,31; 45,92</t>
+          <t>34,72; 45,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,27; 46,55</t>
+          <t>35,91; 46,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,34; 44,54</t>
+          <t>37,07; 44,67</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35,46; 52,38</t>
+          <t>35,77; 51,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37,38; 46,59</t>
+          <t>37,75; 47,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,73; 46,63</t>
+          <t>38,72; 46,41</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,66; 43,24</t>
+          <t>38,05; 43,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,16; 47,02</t>
+          <t>42,44; 47,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,29; 44,61</t>
+          <t>41,16; 44,39</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la mañana</t>
+          <t>Población que, al menos, se cepilla los dientes por la mañana (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>76768; 105808</t>
+          <t>75682; 104805</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53899; 74956</t>
+          <t>53084; 75738</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134609; 175702</t>
+          <t>136588; 171916</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58545; 83830</t>
+          <t>58029; 85166</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68267; 96190</t>
+          <t>67780; 95464</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131178; 171048</t>
+          <t>134530; 172575</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>99323; 132043</t>
+          <t>98423; 131131</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30158; 48202</t>
+          <t>31125; 48066</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137348; 176071</t>
+          <t>136312; 173693</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>222923; 274228</t>
+          <t>221299; 269573</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>183816; 223176</t>
+          <t>183313; 222910</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>416524; 482842</t>
+          <t>416657; 480240</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>118991; 154758</t>
+          <t>117014; 154382</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>146846; 188450</t>
+          <t>145396; 186899</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>277000; 330445</t>
+          <t>275005; 331373</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55650; 82205</t>
+          <t>56134; 81470</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>197271; 245849</t>
+          <t>199185; 248223</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>265158; 319265</t>
+          <t>265098; 317735</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>687172; 768663</t>
+          <t>676341; 764389</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>732841; 817245</t>
+          <t>737572; 822636</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1451649; 1568367</t>
+          <t>1447136; 1560745</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$mañana-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19F$mañana-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,89; 52,47</t>
+          <t>38,63; 52,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,2; 58,79</t>
+          <t>41,23; 58,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,57; 52,32</t>
+          <t>41,59; 53,01</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,39; 47,54</t>
+          <t>32,34; 47,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,77; 53,2</t>
+          <t>37,51; 53,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,51; 48,12</t>
+          <t>37,51; 47,78</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,89; 46,49</t>
+          <t>34,96; 46,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,74; 64,46</t>
+          <t>41,41; 64,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,22; 48,7</t>
+          <t>37,91; 48,74</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,54; 43,29</t>
+          <t>35,09; 43,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,37; 52,73</t>
+          <t>42,63; 52,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,86; 45,94</t>
+          <t>39,81; 46,18</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,72; 45,81</t>
+          <t>35,55; 46,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,91; 46,16</t>
+          <t>35,98; 45,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,07; 44,67</t>
+          <t>37,19; 44,31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35,77; 51,91</t>
+          <t>35,44; 51,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37,75; 47,04</t>
+          <t>38,0; 46,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,72; 46,41</t>
+          <t>38,76; 46,44</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,05; 43,0</t>
+          <t>38,41; 43,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,44; 47,33</t>
+          <t>42,38; 47,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,16; 44,39</t>
+          <t>41,06; 44,57</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75682; 104805</t>
+          <t>77160; 104998</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53084; 75738</t>
+          <t>53120; 75760</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>136588; 171916</t>
+          <t>136648; 174192</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58029; 85166</t>
+          <t>57947; 84505</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67780; 95464</t>
+          <t>67320; 95382</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134530; 172575</t>
+          <t>134509; 171341</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98423; 131131</t>
+          <t>98630; 131477</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31125; 48066</t>
+          <t>30876; 48416</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136312; 173693</t>
+          <t>135220; 173851</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>221299; 269573</t>
+          <t>218527; 268588</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>183313; 222910</t>
+          <t>180196; 222309</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>416657; 480240</t>
+          <t>416212; 482810</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>117014; 154382</t>
+          <t>119797; 155069</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>145396; 186899</t>
+          <t>145649; 185997</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>275005; 331373</t>
+          <t>275928; 328732</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56134; 81470</t>
+          <t>55615; 80647</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>199185; 248223</t>
+          <t>200552; 245543</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>265098; 317735</t>
+          <t>265337; 317934</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>676341; 764389</t>
+          <t>682735; 771532</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>737572; 822636</t>
+          <t>736693; 822285</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1447136; 1560745</t>
+          <t>1443439; 1567144</t>
         </is>
       </c>
     </row>
